--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/NEVADA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/NEVADA_2011.xlsx
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C111">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C158">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C187">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C713">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C778">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C797">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C804">
@@ -15432,7 +15432,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C838">
@@ -20994,7 +20994,7 @@
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1147">
@@ -22866,7 +22866,7 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1251">
